--- a/proposition-normes-standards/ig/StructureDefinition-cds-organization.xlsx
+++ b/proposition-normes-standards/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:41:23+00:00</t>
+    <t>2026-08-28T14:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
